--- a/artfynd/A 16707-2026 artfynd.xlsx
+++ b/artfynd/A 16707-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116059318</v>
+        <v>116059315</v>
       </c>
       <c r="B2" t="n">
-        <v>78576</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>739674</v>
+        <v>739641</v>
       </c>
       <c r="R2" t="n">
-        <v>7346642</v>
+        <v>7346836</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Minst 10 granar med rikligt med ringlav</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,12 +775,7 @@
         <v>116059316</v>
       </c>
       <c r="B3" t="n">
-        <v>78576</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116059324</v>
+        <v>116059317</v>
       </c>
       <c r="B4" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>637</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739716</v>
+        <v>739675</v>
       </c>
       <c r="R4" t="n">
-        <v>7346598</v>
+        <v>7346648</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med ringlav</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116059315</v>
+        <v>116059318</v>
       </c>
       <c r="B5" t="n">
-        <v>78576</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739641</v>
+        <v>739674</v>
       </c>
       <c r="R5" t="n">
-        <v>7346836</v>
+        <v>7346642</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1042,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst 10 granar med rikligt med ringlav</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,37 +1073,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116059317</v>
+        <v>116059324</v>
       </c>
       <c r="B6" t="n">
-        <v>78576</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>637</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>739675</v>
+        <v>739716</v>
       </c>
       <c r="R6" t="n">
-        <v>7346648</v>
+        <v>7346598</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1144,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt med ringlav</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1198,16 +1173,11 @@
         <v>116059323</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1294,6 +1264,103 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>116059330</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skogen, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>740389</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7346566</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-09-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Albin Larsson Ekström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Albin Larsson Ekström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16707-2026 artfynd.xlsx
+++ b/artfynd/A 16707-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116059315</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116059316</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116059317</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116059318</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116059324</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116059323</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1361,8 +1396,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116059330</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>